--- a/Templates/GZ28 V8 SpeedShop INVOICE US.000.1 - BLANK.xlsx
+++ b/Templates/GZ28 V8 SpeedShop INVOICE US.000.1 - BLANK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\gz28-speedshop-control\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C12FEF-9C16-48D7-BD34-3716B157D041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4FA691-D62F-46CA-9C17-1D92C316F99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="583" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,9 +265,6 @@
     <t>Project:</t>
   </si>
   <si>
-    <t>Pack:</t>
-  </si>
-  <si>
     <t>Mileage:</t>
   </si>
   <si>
@@ -325,9 +322,6 @@
     <t>FLORIDA</t>
   </si>
   <si>
-    <t>QUOTE #</t>
-  </si>
-  <si>
     <t>NOTES:</t>
   </si>
   <si>
@@ -389,6 +383,12 @@
   </si>
   <si>
     <t>field 020</t>
+  </si>
+  <si>
+    <t>INVOICE #</t>
+  </si>
+  <si>
+    <t>Sercice:</t>
   </si>
 </sst>
 </file>
@@ -1309,6 +1309,243 @@
     <xf numFmtId="9" fontId="22" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="26" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="26" fillId="11" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="11" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="11" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="26" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1318,12 +1555,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1374,237 +1605,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="26" fillId="11" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="11" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="11" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="11" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="11" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2023,231 +2023,231 @@
   <sheetData>
     <row r="1" spans="2:13" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:13" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="e" vm="1">
+      <c r="B2" s="150" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="J2" s="74" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="J2" s="151" t="s">
+        <v>68</v>
+      </c>
+      <c r="K2" s="152"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="2:13" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="J3" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="75"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" spans="2:13" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="J3" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="78"/>
-      <c r="L3" s="79"/>
+      <c r="K3" s="155"/>
+      <c r="L3" s="156"/>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="2:13" s="26" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
       <c r="I4" s="24"/>
-      <c r="J4" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="81"/>
-      <c r="L4" s="82"/>
+      <c r="J4" s="157" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="158"/>
+      <c r="L4" s="159"/>
       <c r="M4" s="25"/>
     </row>
     <row r="5" spans="2:13" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:13" s="10" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="85"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="162"/>
       <c r="M6" s="11"/>
     </row>
     <row r="7" spans="2:13" s="12" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="88"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="165"/>
       <c r="M7" s="13"/>
     </row>
     <row r="8" spans="2:13" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="2:13" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
+      <c r="B9" s="146" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="148"/>
       <c r="I9" s="27" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K9" s="27" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="2:13" s="2" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="149" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="149"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="149"/>
+      <c r="H10" s="149"/>
       <c r="I10" s="28" t="s">
         <v>20</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K10" s="28" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M10" s="23"/>
     </row>
     <row r="11" spans="2:13" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:13" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="68"/>
+      <c r="C12" s="147"/>
       <c r="D12" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="69" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
+      <c r="H12" s="148" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="148"/>
+      <c r="J12" s="148"/>
       <c r="K12" s="27" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="2:13" s="2" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="145" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="130"/>
+      <c r="D13" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="2:13" s="2" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="34" t="s">
+      <c r="G13" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="33" t="s">
+      <c r="I13" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="33" t="s">
         <v>63</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>65</v>
       </c>
       <c r="K13" s="28" t="s">
         <v>27</v>
       </c>
       <c r="L13" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M13" s="23"/>
     </row>
     <row r="14" spans="2:13" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="2:13" s="15" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="92"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="138"/>
     </row>
     <row r="16" spans="2:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="96"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="142"/>
       <c r="J16" s="18" t="s">
         <v>14</v>
       </c>
@@ -2259,16 +2259,16 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="93" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="89"/>
-      <c r="F17" s="89"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
+      <c r="B17" s="139" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="122"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="122"/>
       <c r="J17" s="21"/>
       <c r="K17" s="20"/>
       <c r="L17" s="65">
@@ -2277,14 +2277,14 @@
       </c>
     </row>
     <row r="18" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="93"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="89"/>
+      <c r="B18" s="139"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="122"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="122"/>
+      <c r="I18" s="122"/>
       <c r="J18" s="21"/>
       <c r="K18" s="20"/>
       <c r="L18" s="65">
@@ -2293,14 +2293,14 @@
       </c>
     </row>
     <row r="19" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="93"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
+      <c r="B19" s="139"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="122"/>
       <c r="J19" s="21"/>
       <c r="K19" s="20"/>
       <c r="L19" s="22">
@@ -2309,14 +2309,14 @@
       </c>
     </row>
     <row r="20" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="93"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="122"/>
+      <c r="I20" s="122"/>
       <c r="J20" s="21"/>
       <c r="K20" s="20"/>
       <c r="L20" s="22">
@@ -2325,14 +2325,14 @@
       </c>
     </row>
     <row r="21" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="93"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="122"/>
+      <c r="I21" s="122"/>
       <c r="J21" s="21"/>
       <c r="K21" s="20"/>
       <c r="L21" s="22">
@@ -2341,14 +2341,14 @@
       </c>
     </row>
     <row r="22" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="93"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
+      <c r="B22" s="139"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="122"/>
+      <c r="I22" s="122"/>
       <c r="J22" s="21"/>
       <c r="K22" s="20"/>
       <c r="L22" s="22">
@@ -2357,14 +2357,14 @@
       </c>
     </row>
     <row r="23" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="93"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
+      <c r="B23" s="139"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="122"/>
+      <c r="I23" s="122"/>
       <c r="J23" s="21"/>
       <c r="K23" s="20"/>
       <c r="L23" s="22">
@@ -2373,14 +2373,14 @@
       </c>
     </row>
     <row r="24" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="93"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
+      <c r="B24" s="139"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
       <c r="J24" s="21"/>
       <c r="K24" s="20"/>
       <c r="L24" s="22">
@@ -2389,14 +2389,14 @@
       </c>
     </row>
     <row r="25" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="93"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89"/>
-      <c r="E25" s="89"/>
-      <c r="F25" s="89"/>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
+      <c r="B25" s="139"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="122"/>
+      <c r="I25" s="122"/>
       <c r="J25" s="21"/>
       <c r="K25" s="20"/>
       <c r="L25" s="22">
@@ -2405,14 +2405,14 @@
       </c>
     </row>
     <row r="26" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="93"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="89"/>
+      <c r="B26" s="139"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="122"/>
+      <c r="H26" s="122"/>
+      <c r="I26" s="122"/>
       <c r="J26" s="21"/>
       <c r="K26" s="20"/>
       <c r="L26" s="22">
@@ -2421,14 +2421,14 @@
       </c>
     </row>
     <row r="27" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="93"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="122"/>
       <c r="J27" s="21"/>
       <c r="K27" s="20"/>
       <c r="L27" s="22">
@@ -2437,14 +2437,14 @@
       </c>
     </row>
     <row r="28" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="93"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
+      <c r="B28" s="139"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="122"/>
+      <c r="I28" s="122"/>
       <c r="J28" s="21"/>
       <c r="K28" s="20"/>
       <c r="L28" s="22">
@@ -2453,14 +2453,14 @@
       </c>
     </row>
     <row r="29" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="93"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
+      <c r="B29" s="139"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122"/>
+      <c r="I29" s="122"/>
       <c r="J29" s="21"/>
       <c r="K29" s="20"/>
       <c r="L29" s="22">
@@ -2469,14 +2469,14 @@
       </c>
     </row>
     <row r="30" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="93"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
+      <c r="B30" s="139"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="122"/>
+      <c r="I30" s="122"/>
       <c r="J30" s="21"/>
       <c r="K30" s="20"/>
       <c r="L30" s="22">
@@ -2485,14 +2485,14 @@
       </c>
     </row>
     <row r="31" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="93"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="122"/>
       <c r="J31" s="21"/>
       <c r="K31" s="20"/>
       <c r="L31" s="22">
@@ -2501,14 +2501,14 @@
       </c>
     </row>
     <row r="32" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="93"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
+      <c r="B32" s="139"/>
+      <c r="C32" s="122"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="122"/>
       <c r="J32" s="21"/>
       <c r="K32" s="20"/>
       <c r="L32" s="22">
@@ -2517,14 +2517,14 @@
       </c>
     </row>
     <row r="33" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="93"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="122"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="122"/>
+      <c r="I33" s="122"/>
       <c r="J33" s="21"/>
       <c r="K33" s="20"/>
       <c r="L33" s="22">
@@ -2533,14 +2533,14 @@
       </c>
     </row>
     <row r="34" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="93"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="122"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="122"/>
+      <c r="I34" s="122"/>
       <c r="J34" s="21"/>
       <c r="K34" s="20"/>
       <c r="L34" s="22">
@@ -2549,14 +2549,14 @@
       </c>
     </row>
     <row r="35" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="93"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
+      <c r="B35" s="139"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="122"/>
       <c r="J35" s="21"/>
       <c r="K35" s="20"/>
       <c r="L35" s="22">
@@ -2565,14 +2565,14 @@
       </c>
     </row>
     <row r="36" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="93"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="89"/>
+      <c r="B36" s="139"/>
+      <c r="C36" s="122"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
       <c r="J36" s="21"/>
       <c r="K36" s="20"/>
       <c r="L36" s="22">
@@ -2581,14 +2581,14 @@
       </c>
     </row>
     <row r="37" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="93"/>
-      <c r="C37" s="89"/>
-      <c r="D37" s="89"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
+      <c r="B37" s="139"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="122"/>
       <c r="J37" s="21"/>
       <c r="K37" s="20"/>
       <c r="L37" s="22">
@@ -2597,14 +2597,14 @@
       </c>
     </row>
     <row r="38" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="93"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="89"/>
+      <c r="B38" s="139"/>
+      <c r="C38" s="122"/>
+      <c r="D38" s="122"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="122"/>
+      <c r="I38" s="122"/>
       <c r="J38" s="21"/>
       <c r="K38" s="20"/>
       <c r="L38" s="22">
@@ -2613,14 +2613,14 @@
       </c>
     </row>
     <row r="39" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="93"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="89"/>
+      <c r="B39" s="139"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
       <c r="J39" s="21"/>
       <c r="K39" s="20"/>
       <c r="L39" s="22">
@@ -2629,35 +2629,35 @@
       </c>
     </row>
     <row r="40" spans="2:12" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="97" t="s">
+      <c r="B40" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="98"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="98"/>
-      <c r="G40" s="98"/>
-      <c r="H40" s="98"/>
-      <c r="I40" s="98"/>
-      <c r="J40" s="98"/>
-      <c r="K40" s="98"/>
+      <c r="C40" s="144"/>
+      <c r="D40" s="144"/>
+      <c r="E40" s="144"/>
+      <c r="F40" s="144"/>
+      <c r="G40" s="144"/>
+      <c r="H40" s="144"/>
+      <c r="I40" s="144"/>
+      <c r="J40" s="144"/>
+      <c r="K40" s="144"/>
       <c r="L40" s="35">
         <f>SUM(L17:L39)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:12" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="99" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="100"/>
-      <c r="D41" s="100"/>
-      <c r="E41" s="100"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="100"/>
-      <c r="J41" s="100"/>
+      <c r="B41" s="134" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
+      <c r="E41" s="135"/>
+      <c r="F41" s="135"/>
+      <c r="G41" s="135"/>
+      <c r="H41" s="135"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
       <c r="K41" s="53">
         <v>6.5000000000000002E-2</v>
       </c>
@@ -2667,18 +2667,18 @@
       </c>
     </row>
     <row r="42" spans="2:12" s="16" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="101" t="s">
+      <c r="B42" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="102"/>
-      <c r="D42" s="102"/>
-      <c r="E42" s="102"/>
-      <c r="F42" s="102"/>
-      <c r="G42" s="102"/>
-      <c r="H42" s="102"/>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="102"/>
+      <c r="C42" s="124"/>
+      <c r="D42" s="124"/>
+      <c r="E42" s="124"/>
+      <c r="F42" s="124"/>
+      <c r="G42" s="124"/>
+      <c r="H42" s="124"/>
+      <c r="I42" s="124"/>
+      <c r="J42" s="124"/>
+      <c r="K42" s="124"/>
       <c r="L42" s="37">
         <f>SUM(L40:L41)</f>
         <v>0</v>
@@ -2686,31 +2686,31 @@
     </row>
     <row r="43" spans="2:12" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="44" spans="2:12" s="15" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="91"/>
-      <c r="G44" s="91"/>
-      <c r="H44" s="91"/>
-      <c r="I44" s="91"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="91"/>
-      <c r="L44" s="92"/>
+      <c r="B44" s="136" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="137"/>
+      <c r="J44" s="137"/>
+      <c r="K44" s="137"/>
+      <c r="L44" s="138"/>
     </row>
     <row r="45" spans="2:12" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="94" t="s">
+      <c r="B45" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="95"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="95"/>
-      <c r="H45" s="95"/>
-      <c r="I45" s="96"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="141"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="141"/>
+      <c r="I45" s="142"/>
       <c r="J45" s="18" t="s">
         <v>14</v>
       </c>
@@ -2722,16 +2722,16 @@
       </c>
     </row>
     <row r="46" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="93" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="89"/>
-      <c r="I46" s="89"/>
+      <c r="B46" s="139" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="122"/>
+      <c r="D46" s="122"/>
+      <c r="E46" s="122"/>
+      <c r="F46" s="122"/>
+      <c r="G46" s="122"/>
+      <c r="H46" s="122"/>
+      <c r="I46" s="122"/>
       <c r="J46" s="21"/>
       <c r="K46" s="20"/>
       <c r="L46" s="22">
@@ -2740,14 +2740,14 @@
       </c>
     </row>
     <row r="47" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="93"/>
-      <c r="C47" s="89"/>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
-      <c r="I47" s="89"/>
+      <c r="B47" s="139"/>
+      <c r="C47" s="122"/>
+      <c r="D47" s="122"/>
+      <c r="E47" s="122"/>
+      <c r="F47" s="122"/>
+      <c r="G47" s="122"/>
+      <c r="H47" s="122"/>
+      <c r="I47" s="122"/>
       <c r="J47" s="21"/>
       <c r="K47" s="20"/>
       <c r="L47" s="22">
@@ -2756,14 +2756,14 @@
       </c>
     </row>
     <row r="48" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="93"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="89"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="89"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="89"/>
-      <c r="I48" s="89"/>
+      <c r="B48" s="139"/>
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+      <c r="F48" s="122"/>
+      <c r="G48" s="122"/>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
       <c r="J48" s="21"/>
       <c r="K48" s="20"/>
       <c r="L48" s="22">
@@ -2772,14 +2772,14 @@
       </c>
     </row>
     <row r="49" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="93"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
+      <c r="B49" s="139"/>
+      <c r="C49" s="122"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="122"/>
+      <c r="F49" s="122"/>
+      <c r="G49" s="122"/>
+      <c r="H49" s="122"/>
+      <c r="I49" s="122"/>
       <c r="J49" s="21"/>
       <c r="K49" s="20"/>
       <c r="L49" s="22">
@@ -2788,14 +2788,14 @@
       </c>
     </row>
     <row r="50" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="93"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="89"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="89"/>
+      <c r="B50" s="139"/>
+      <c r="C50" s="122"/>
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="122"/>
+      <c r="H50" s="122"/>
+      <c r="I50" s="122"/>
       <c r="J50" s="21"/>
       <c r="K50" s="20"/>
       <c r="L50" s="22">
@@ -2804,14 +2804,14 @@
       </c>
     </row>
     <row r="51" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="93"/>
-      <c r="C51" s="89"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="89"/>
+      <c r="B51" s="139"/>
+      <c r="C51" s="122"/>
+      <c r="D51" s="122"/>
+      <c r="E51" s="122"/>
+      <c r="F51" s="122"/>
+      <c r="G51" s="122"/>
+      <c r="H51" s="122"/>
+      <c r="I51" s="122"/>
       <c r="J51" s="21"/>
       <c r="K51" s="20"/>
       <c r="L51" s="22">
@@ -2820,14 +2820,14 @@
       </c>
     </row>
     <row r="52" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="93"/>
-      <c r="C52" s="89"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="89"/>
-      <c r="G52" s="89"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="89"/>
+      <c r="B52" s="139"/>
+      <c r="C52" s="122"/>
+      <c r="D52" s="122"/>
+      <c r="E52" s="122"/>
+      <c r="F52" s="122"/>
+      <c r="G52" s="122"/>
+      <c r="H52" s="122"/>
+      <c r="I52" s="122"/>
       <c r="J52" s="21"/>
       <c r="K52" s="20"/>
       <c r="L52" s="22">
@@ -2836,14 +2836,14 @@
       </c>
     </row>
     <row r="53" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="93"/>
-      <c r="C53" s="89"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="89"/>
-      <c r="F53" s="89"/>
-      <c r="G53" s="89"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="89"/>
+      <c r="B53" s="139"/>
+      <c r="C53" s="122"/>
+      <c r="D53" s="122"/>
+      <c r="E53" s="122"/>
+      <c r="F53" s="122"/>
+      <c r="G53" s="122"/>
+      <c r="H53" s="122"/>
+      <c r="I53" s="122"/>
       <c r="J53" s="21"/>
       <c r="K53" s="20"/>
       <c r="L53" s="22">
@@ -2852,14 +2852,14 @@
       </c>
     </row>
     <row r="54" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="93"/>
-      <c r="C54" s="89"/>
-      <c r="D54" s="89"/>
-      <c r="E54" s="89"/>
-      <c r="F54" s="89"/>
-      <c r="G54" s="89"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="89"/>
+      <c r="B54" s="139"/>
+      <c r="C54" s="122"/>
+      <c r="D54" s="122"/>
+      <c r="E54" s="122"/>
+      <c r="F54" s="122"/>
+      <c r="G54" s="122"/>
+      <c r="H54" s="122"/>
+      <c r="I54" s="122"/>
       <c r="J54" s="21"/>
       <c r="K54" s="20"/>
       <c r="L54" s="22">
@@ -2868,14 +2868,14 @@
       </c>
     </row>
     <row r="55" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="93"/>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89"/>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
-      <c r="G55" s="89"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="89"/>
+      <c r="B55" s="139"/>
+      <c r="C55" s="122"/>
+      <c r="D55" s="122"/>
+      <c r="E55" s="122"/>
+      <c r="F55" s="122"/>
+      <c r="G55" s="122"/>
+      <c r="H55" s="122"/>
+      <c r="I55" s="122"/>
       <c r="J55" s="21"/>
       <c r="K55" s="20"/>
       <c r="L55" s="22">
@@ -2884,14 +2884,14 @@
       </c>
     </row>
     <row r="56" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="93"/>
-      <c r="C56" s="89"/>
-      <c r="D56" s="89"/>
-      <c r="E56" s="89"/>
-      <c r="F56" s="89"/>
-      <c r="G56" s="89"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="89"/>
+      <c r="B56" s="139"/>
+      <c r="C56" s="122"/>
+      <c r="D56" s="122"/>
+      <c r="E56" s="122"/>
+      <c r="F56" s="122"/>
+      <c r="G56" s="122"/>
+      <c r="H56" s="122"/>
+      <c r="I56" s="122"/>
       <c r="J56" s="21"/>
       <c r="K56" s="20"/>
       <c r="L56" s="22">
@@ -2900,14 +2900,14 @@
       </c>
     </row>
     <row r="57" spans="2:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="93"/>
-      <c r="C57" s="89"/>
-      <c r="D57" s="89"/>
-      <c r="E57" s="89"/>
-      <c r="F57" s="89"/>
-      <c r="G57" s="89"/>
-      <c r="H57" s="89"/>
-      <c r="I57" s="89"/>
+      <c r="B57" s="139"/>
+      <c r="C57" s="122"/>
+      <c r="D57" s="122"/>
+      <c r="E57" s="122"/>
+      <c r="F57" s="122"/>
+      <c r="G57" s="122"/>
+      <c r="H57" s="122"/>
+      <c r="I57" s="122"/>
       <c r="J57" s="21"/>
       <c r="K57" s="20"/>
       <c r="L57" s="22">
@@ -2916,18 +2916,18 @@
       </c>
     </row>
     <row r="58" spans="2:12" s="16" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="101" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="102"/>
-      <c r="D58" s="102"/>
-      <c r="E58" s="102"/>
-      <c r="F58" s="102"/>
-      <c r="G58" s="102"/>
-      <c r="H58" s="102"/>
-      <c r="I58" s="102"/>
-      <c r="J58" s="102"/>
-      <c r="K58" s="102"/>
+      <c r="B58" s="123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="124"/>
+      <c r="D58" s="124"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="124"/>
+      <c r="G58" s="124"/>
+      <c r="H58" s="124"/>
+      <c r="I58" s="124"/>
+      <c r="J58" s="124"/>
+      <c r="K58" s="124"/>
       <c r="L58" s="37">
         <f>SUM(L46:L57)</f>
         <v>0</v>
@@ -2935,53 +2935,53 @@
     </row>
     <row r="59" spans="2:12" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="60" spans="2:12" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="108" t="s">
-        <v>34</v>
-      </c>
-      <c r="C60" s="109"/>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="109"/>
+      <c r="B60" s="125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="126"/>
+      <c r="D60" s="126"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="126"/>
+      <c r="I60" s="126"/>
+      <c r="J60" s="126"/>
+      <c r="K60" s="126"/>
       <c r="L60" s="46">
         <f>L42+L58</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="2:12" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" s="111"/>
-      <c r="D61" s="111"/>
-      <c r="E61" s="111"/>
-      <c r="F61" s="111"/>
-      <c r="G61" s="111"/>
-      <c r="H61" s="111"/>
-      <c r="I61" s="111"/>
-      <c r="J61" s="111"/>
-      <c r="K61" s="111"/>
+      <c r="B61" s="127" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="128"/>
+      <c r="D61" s="128"/>
+      <c r="E61" s="128"/>
+      <c r="F61" s="128"/>
+      <c r="G61" s="128"/>
+      <c r="H61" s="128"/>
+      <c r="I61" s="128"/>
+      <c r="J61" s="128"/>
+      <c r="K61" s="128"/>
       <c r="L61" s="66">
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:12" s="17" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="112" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="71"/>
-      <c r="F62" s="71"/>
-      <c r="G62" s="71"/>
-      <c r="H62" s="71"/>
-      <c r="I62" s="71"/>
-      <c r="J62" s="71"/>
-      <c r="K62" s="71"/>
+      <c r="B62" s="129" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="130"/>
+      <c r="D62" s="130"/>
+      <c r="E62" s="130"/>
+      <c r="F62" s="130"/>
+      <c r="G62" s="130"/>
+      <c r="H62" s="130"/>
+      <c r="I62" s="130"/>
+      <c r="J62" s="130"/>
+      <c r="K62" s="130"/>
       <c r="L62" s="38">
         <f>L60+L60*L61</f>
         <v>0</v>
@@ -2989,168 +2989,168 @@
     </row>
     <row r="63" spans="2:12" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="2:12" s="39" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="113" t="s">
-        <v>36</v>
-      </c>
-      <c r="C64" s="114"/>
-      <c r="D64" s="114"/>
-      <c r="E64" s="114"/>
-      <c r="F64" s="114"/>
-      <c r="G64" s="114"/>
-      <c r="H64" s="114"/>
-      <c r="I64" s="114"/>
-      <c r="J64" s="114"/>
-      <c r="K64" s="114"/>
-      <c r="L64" s="115"/>
+      <c r="B64" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="132"/>
+      <c r="D64" s="132"/>
+      <c r="E64" s="132"/>
+      <c r="F64" s="132"/>
+      <c r="G64" s="132"/>
+      <c r="H64" s="132"/>
+      <c r="I64" s="132"/>
+      <c r="J64" s="132"/>
+      <c r="K64" s="132"/>
+      <c r="L64" s="133"/>
     </row>
     <row r="65" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="103"/>
-      <c r="C65" s="104"/>
-      <c r="D65" s="104"/>
-      <c r="E65" s="105"/>
-      <c r="F65" s="106"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="106"/>
-      <c r="I65" s="106"/>
-      <c r="J65" s="106"/>
-      <c r="K65" s="107"/>
+      <c r="B65" s="117"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="118"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="120"/>
+      <c r="H65" s="120"/>
+      <c r="I65" s="120"/>
+      <c r="J65" s="120"/>
+      <c r="K65" s="121"/>
       <c r="L65" s="44"/>
     </row>
     <row r="66" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="103"/>
-      <c r="C66" s="104"/>
-      <c r="D66" s="104"/>
-      <c r="E66" s="105"/>
-      <c r="F66" s="106"/>
-      <c r="G66" s="106"/>
-      <c r="H66" s="106"/>
-      <c r="I66" s="106"/>
-      <c r="J66" s="106"/>
-      <c r="K66" s="107"/>
+      <c r="B66" s="117"/>
+      <c r="C66" s="118"/>
+      <c r="D66" s="118"/>
+      <c r="E66" s="119"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="120"/>
+      <c r="H66" s="120"/>
+      <c r="I66" s="120"/>
+      <c r="J66" s="120"/>
+      <c r="K66" s="121"/>
       <c r="L66" s="44"/>
     </row>
     <row r="67" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="103"/>
-      <c r="C67" s="104"/>
-      <c r="D67" s="104"/>
-      <c r="E67" s="105"/>
-      <c r="F67" s="106"/>
-      <c r="G67" s="106"/>
-      <c r="H67" s="106"/>
-      <c r="I67" s="106"/>
-      <c r="J67" s="106"/>
-      <c r="K67" s="107"/>
+      <c r="B67" s="117"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="118"/>
+      <c r="E67" s="119"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="120"/>
+      <c r="H67" s="120"/>
+      <c r="I67" s="120"/>
+      <c r="J67" s="120"/>
+      <c r="K67" s="121"/>
       <c r="L67" s="44"/>
     </row>
     <row r="68" spans="2:13" s="43" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="103"/>
-      <c r="C68" s="104"/>
-      <c r="D68" s="104"/>
-      <c r="E68" s="105"/>
-      <c r="F68" s="106"/>
-      <c r="G68" s="106"/>
-      <c r="H68" s="106"/>
-      <c r="I68" s="106"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="107"/>
+      <c r="B68" s="117"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="118"/>
+      <c r="E68" s="119"/>
+      <c r="F68" s="120"/>
+      <c r="G68" s="120"/>
+      <c r="H68" s="120"/>
+      <c r="I68" s="120"/>
+      <c r="J68" s="120"/>
+      <c r="K68" s="121"/>
       <c r="L68" s="44"/>
     </row>
     <row r="69" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="103"/>
-      <c r="C69" s="104"/>
-      <c r="D69" s="104"/>
-      <c r="E69" s="105"/>
-      <c r="F69" s="106"/>
-      <c r="G69" s="106"/>
-      <c r="H69" s="106"/>
-      <c r="I69" s="106"/>
-      <c r="J69" s="106"/>
-      <c r="K69" s="107"/>
+      <c r="B69" s="117"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="120"/>
+      <c r="G69" s="120"/>
+      <c r="H69" s="120"/>
+      <c r="I69" s="120"/>
+      <c r="J69" s="120"/>
+      <c r="K69" s="121"/>
       <c r="L69" s="44"/>
     </row>
     <row r="70" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="103"/>
-      <c r="C70" s="104"/>
-      <c r="D70" s="104"/>
-      <c r="E70" s="105"/>
-      <c r="F70" s="106"/>
-      <c r="G70" s="106"/>
-      <c r="H70" s="106"/>
-      <c r="I70" s="106"/>
-      <c r="J70" s="106"/>
-      <c r="K70" s="107"/>
+      <c r="B70" s="117"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="118"/>
+      <c r="E70" s="119"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="120"/>
+      <c r="H70" s="120"/>
+      <c r="I70" s="120"/>
+      <c r="J70" s="120"/>
+      <c r="K70" s="121"/>
       <c r="L70" s="44"/>
     </row>
     <row r="71" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="103"/>
-      <c r="C71" s="104"/>
-      <c r="D71" s="104"/>
-      <c r="E71" s="105"/>
-      <c r="F71" s="106"/>
-      <c r="G71" s="106"/>
-      <c r="H71" s="106"/>
-      <c r="I71" s="106"/>
-      <c r="J71" s="106"/>
-      <c r="K71" s="107"/>
+      <c r="B71" s="117"/>
+      <c r="C71" s="118"/>
+      <c r="D71" s="118"/>
+      <c r="E71" s="119"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="120"/>
+      <c r="H71" s="120"/>
+      <c r="I71" s="120"/>
+      <c r="J71" s="120"/>
+      <c r="K71" s="121"/>
       <c r="L71" s="44"/>
     </row>
     <row r="72" spans="2:13" s="43" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="103"/>
-      <c r="C72" s="104"/>
-      <c r="D72" s="104"/>
-      <c r="E72" s="105"/>
-      <c r="F72" s="106"/>
-      <c r="G72" s="106"/>
-      <c r="H72" s="106"/>
-      <c r="I72" s="106"/>
-      <c r="J72" s="106"/>
-      <c r="K72" s="107"/>
+      <c r="B72" s="117"/>
+      <c r="C72" s="118"/>
+      <c r="D72" s="118"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="120"/>
+      <c r="H72" s="120"/>
+      <c r="I72" s="120"/>
+      <c r="J72" s="120"/>
+      <c r="K72" s="121"/>
       <c r="L72" s="44"/>
     </row>
     <row r="73" spans="2:13" s="43" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="103"/>
-      <c r="C73" s="104"/>
-      <c r="D73" s="104"/>
-      <c r="E73" s="105"/>
-      <c r="F73" s="106"/>
-      <c r="G73" s="106"/>
-      <c r="H73" s="106"/>
-      <c r="I73" s="106"/>
-      <c r="J73" s="106"/>
-      <c r="K73" s="107"/>
+      <c r="B73" s="117"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="118"/>
+      <c r="E73" s="119"/>
+      <c r="F73" s="120"/>
+      <c r="G73" s="120"/>
+      <c r="H73" s="120"/>
+      <c r="I73" s="120"/>
+      <c r="J73" s="120"/>
+      <c r="K73" s="121"/>
       <c r="L73" s="44"/>
     </row>
     <row r="74" spans="2:13" s="39" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="126" t="s">
-        <v>43</v>
-      </c>
-      <c r="C74" s="127"/>
-      <c r="D74" s="127"/>
-      <c r="E74" s="127"/>
-      <c r="F74" s="127"/>
-      <c r="G74" s="127"/>
-      <c r="H74" s="127"/>
-      <c r="I74" s="127"/>
-      <c r="J74" s="127"/>
-      <c r="K74" s="127"/>
+      <c r="B74" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" s="105"/>
+      <c r="D74" s="105"/>
+      <c r="E74" s="105"/>
+      <c r="F74" s="105"/>
+      <c r="G74" s="105"/>
+      <c r="H74" s="105"/>
+      <c r="I74" s="105"/>
+      <c r="J74" s="105"/>
+      <c r="K74" s="105"/>
       <c r="L74" s="54">
         <f>SUM(L65:L73)</f>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:13" s="39" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="128" t="s">
+      <c r="B75" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C75" s="129"/>
-      <c r="D75" s="129"/>
-      <c r="E75" s="129"/>
-      <c r="F75" s="129"/>
-      <c r="G75" s="129"/>
-      <c r="H75" s="129"/>
-      <c r="I75" s="129"/>
-      <c r="J75" s="129"/>
-      <c r="K75" s="129"/>
+      <c r="C75" s="107"/>
+      <c r="D75" s="107"/>
+      <c r="E75" s="107"/>
+      <c r="F75" s="107"/>
+      <c r="G75" s="107"/>
+      <c r="H75" s="107"/>
+      <c r="I75" s="107"/>
+      <c r="J75" s="107"/>
+      <c r="K75" s="107"/>
       <c r="L75" s="45">
         <f>L62-SUM(L65:L73)</f>
         <v>0</v>
@@ -3169,103 +3169,103 @@
       <c r="M76" s="42"/>
     </row>
     <row r="77" spans="2:13" s="47" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="130" t="s">
-        <v>49</v>
-      </c>
-      <c r="C77" s="131"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="131"/>
-      <c r="F77" s="131"/>
-      <c r="G77" s="131"/>
-      <c r="H77" s="131"/>
-      <c r="I77" s="131"/>
-      <c r="J77" s="131"/>
-      <c r="K77" s="131"/>
-      <c r="L77" s="132"/>
+      <c r="B77" s="108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="109"/>
+      <c r="D77" s="109"/>
+      <c r="E77" s="109"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109"/>
+      <c r="I77" s="109"/>
+      <c r="J77" s="109"/>
+      <c r="K77" s="109"/>
+      <c r="L77" s="110"/>
       <c r="M77" s="48"/>
     </row>
-    <row r="78" spans="2:13" s="161" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="162"/>
-      <c r="C78" s="163"/>
-      <c r="D78" s="163"/>
-      <c r="E78" s="163"/>
-      <c r="F78" s="163"/>
-      <c r="G78" s="163"/>
-      <c r="H78" s="163"/>
-      <c r="I78" s="163"/>
-      <c r="J78" s="163"/>
-      <c r="K78" s="163"/>
-      <c r="L78" s="164"/>
-      <c r="M78" s="165"/>
-    </row>
-    <row r="79" spans="2:13" s="161" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="162"/>
-      <c r="C79" s="163"/>
-      <c r="D79" s="163"/>
-      <c r="E79" s="163"/>
-      <c r="F79" s="163"/>
-      <c r="G79" s="163"/>
-      <c r="H79" s="163"/>
-      <c r="I79" s="163"/>
-      <c r="J79" s="163"/>
-      <c r="K79" s="163"/>
-      <c r="L79" s="164"/>
-      <c r="M79" s="165"/>
-    </row>
-    <row r="80" spans="2:13" s="161" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="162"/>
-      <c r="C80" s="163"/>
-      <c r="D80" s="163"/>
-      <c r="E80" s="163"/>
-      <c r="F80" s="163"/>
-      <c r="G80" s="163"/>
-      <c r="H80" s="163"/>
-      <c r="I80" s="163"/>
-      <c r="J80" s="163"/>
-      <c r="K80" s="163"/>
-      <c r="L80" s="164"/>
-      <c r="M80" s="165"/>
-    </row>
-    <row r="81" spans="2:13" s="161" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="162"/>
-      <c r="C81" s="163"/>
-      <c r="D81" s="163"/>
-      <c r="E81" s="163"/>
-      <c r="F81" s="163"/>
-      <c r="G81" s="163"/>
-      <c r="H81" s="163"/>
-      <c r="I81" s="163"/>
-      <c r="J81" s="163"/>
-      <c r="K81" s="163"/>
-      <c r="L81" s="164"/>
-      <c r="M81" s="165"/>
-    </row>
-    <row r="82" spans="2:13" s="161" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="162"/>
-      <c r="C82" s="163"/>
-      <c r="D82" s="163"/>
-      <c r="E82" s="163"/>
-      <c r="F82" s="163"/>
-      <c r="G82" s="163"/>
-      <c r="H82" s="163"/>
-      <c r="I82" s="163"/>
-      <c r="J82" s="163"/>
-      <c r="K82" s="163"/>
-      <c r="L82" s="164"/>
-      <c r="M82" s="165"/>
+    <row r="78" spans="2:13" s="67" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="114"/>
+      <c r="C78" s="115"/>
+      <c r="D78" s="115"/>
+      <c r="E78" s="115"/>
+      <c r="F78" s="115"/>
+      <c r="G78" s="115"/>
+      <c r="H78" s="115"/>
+      <c r="I78" s="115"/>
+      <c r="J78" s="115"/>
+      <c r="K78" s="115"/>
+      <c r="L78" s="116"/>
+      <c r="M78" s="68"/>
+    </row>
+    <row r="79" spans="2:13" s="67" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="114"/>
+      <c r="C79" s="115"/>
+      <c r="D79" s="115"/>
+      <c r="E79" s="115"/>
+      <c r="F79" s="115"/>
+      <c r="G79" s="115"/>
+      <c r="H79" s="115"/>
+      <c r="I79" s="115"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="115"/>
+      <c r="L79" s="116"/>
+      <c r="M79" s="68"/>
+    </row>
+    <row r="80" spans="2:13" s="67" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="114"/>
+      <c r="C80" s="115"/>
+      <c r="D80" s="115"/>
+      <c r="E80" s="115"/>
+      <c r="F80" s="115"/>
+      <c r="G80" s="115"/>
+      <c r="H80" s="115"/>
+      <c r="I80" s="115"/>
+      <c r="J80" s="115"/>
+      <c r="K80" s="115"/>
+      <c r="L80" s="116"/>
+      <c r="M80" s="68"/>
+    </row>
+    <row r="81" spans="2:13" s="67" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="114"/>
+      <c r="C81" s="115"/>
+      <c r="D81" s="115"/>
+      <c r="E81" s="115"/>
+      <c r="F81" s="115"/>
+      <c r="G81" s="115"/>
+      <c r="H81" s="115"/>
+      <c r="I81" s="115"/>
+      <c r="J81" s="115"/>
+      <c r="K81" s="115"/>
+      <c r="L81" s="116"/>
+      <c r="M81" s="68"/>
+    </row>
+    <row r="82" spans="2:13" s="67" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="114"/>
+      <c r="C82" s="115"/>
+      <c r="D82" s="115"/>
+      <c r="E82" s="115"/>
+      <c r="F82" s="115"/>
+      <c r="G82" s="115"/>
+      <c r="H82" s="115"/>
+      <c r="I82" s="115"/>
+      <c r="J82" s="115"/>
+      <c r="K82" s="115"/>
+      <c r="L82" s="116"/>
+      <c r="M82" s="68"/>
     </row>
     <row r="83" spans="2:13" s="51" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="116"/>
-      <c r="C83" s="117"/>
-      <c r="D83" s="117"/>
-      <c r="E83" s="117"/>
-      <c r="F83" s="117"/>
-      <c r="G83" s="117"/>
-      <c r="H83" s="117"/>
-      <c r="I83" s="117"/>
-      <c r="J83" s="117"/>
-      <c r="K83" s="117"/>
-      <c r="L83" s="118"/>
+      <c r="B83" s="94"/>
+      <c r="C83" s="95"/>
+      <c r="D83" s="95"/>
+      <c r="E83" s="95"/>
+      <c r="F83" s="95"/>
+      <c r="G83" s="95"/>
+      <c r="H83" s="95"/>
+      <c r="I83" s="95"/>
+      <c r="J83" s="95"/>
+      <c r="K83" s="95"/>
+      <c r="L83" s="96"/>
       <c r="M83" s="52"/>
     </row>
     <row r="84" spans="2:13" s="4" customFormat="1" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -3281,55 +3281,55 @@
       <c r="M84" s="42"/>
     </row>
     <row r="85" spans="2:13" s="47" customFormat="1" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="130" t="s">
+      <c r="B85" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C85" s="109"/>
+      <c r="D85" s="109"/>
+      <c r="E85" s="109"/>
+      <c r="F85" s="109"/>
+      <c r="G85" s="110"/>
+      <c r="H85" s="108" t="s">
+        <v>36</v>
+      </c>
+      <c r="I85" s="109"/>
+      <c r="J85" s="109"/>
+      <c r="K85" s="109"/>
+      <c r="L85" s="110"/>
+      <c r="M85" s="48"/>
+    </row>
+    <row r="86" spans="2:13" s="49" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B86" s="111" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" s="112"/>
+      <c r="D86" s="112"/>
+      <c r="E86" s="112"/>
+      <c r="F86" s="112"/>
+      <c r="G86" s="113"/>
+      <c r="H86" s="111" t="s">
+        <v>39</v>
+      </c>
+      <c r="I86" s="112"/>
+      <c r="J86" s="112"/>
+      <c r="K86" s="112"/>
+      <c r="L86" s="113"/>
+      <c r="M86" s="50"/>
+    </row>
+    <row r="87" spans="2:13" s="51" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="94"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="95"/>
+      <c r="E87" s="95"/>
+      <c r="F87" s="95"/>
+      <c r="G87" s="96"/>
+      <c r="H87" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="C85" s="131"/>
-      <c r="D85" s="131"/>
-      <c r="E85" s="131"/>
-      <c r="F85" s="131"/>
-      <c r="G85" s="132"/>
-      <c r="H85" s="130" t="s">
-        <v>37</v>
-      </c>
-      <c r="I85" s="131"/>
-      <c r="J85" s="131"/>
-      <c r="K85" s="131"/>
-      <c r="L85" s="132"/>
-      <c r="M85" s="48"/>
-    </row>
-    <row r="86" spans="2:13" s="49" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B86" s="133" t="s">
-        <v>69</v>
-      </c>
-      <c r="C86" s="134"/>
-      <c r="D86" s="134"/>
-      <c r="E86" s="134"/>
-      <c r="F86" s="134"/>
-      <c r="G86" s="135"/>
-      <c r="H86" s="133" t="s">
-        <v>40</v>
-      </c>
-      <c r="I86" s="134"/>
-      <c r="J86" s="134"/>
-      <c r="K86" s="134"/>
-      <c r="L86" s="135"/>
-      <c r="M86" s="50"/>
-    </row>
-    <row r="87" spans="2:13" s="51" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="116"/>
-      <c r="C87" s="117"/>
-      <c r="D87" s="117"/>
-      <c r="E87" s="117"/>
-      <c r="F87" s="117"/>
-      <c r="G87" s="118"/>
-      <c r="H87" s="116" t="s">
-        <v>39</v>
-      </c>
-      <c r="I87" s="117"/>
-      <c r="J87" s="117"/>
-      <c r="K87" s="117"/>
-      <c r="L87" s="118"/>
+      <c r="I87" s="95"/>
+      <c r="J87" s="95"/>
+      <c r="K87" s="95"/>
+      <c r="L87" s="96"/>
       <c r="M87" s="52"/>
     </row>
     <row r="89" spans="2:13" s="61" customFormat="1" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3340,414 +3340,414 @@
     </row>
     <row r="90" spans="2:13" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="2:13" s="10" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="119" t="s">
-        <v>45</v>
-      </c>
-      <c r="C91" s="120"/>
-      <c r="D91" s="120"/>
-      <c r="E91" s="120"/>
-      <c r="F91" s="120"/>
-      <c r="G91" s="120"/>
-      <c r="H91" s="120"/>
-      <c r="I91" s="120"/>
-      <c r="J91" s="120"/>
-      <c r="K91" s="120"/>
-      <c r="L91" s="121"/>
+      <c r="B91" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" s="98"/>
+      <c r="D91" s="98"/>
+      <c r="E91" s="98"/>
+      <c r="F91" s="98"/>
+      <c r="G91" s="98"/>
+      <c r="H91" s="98"/>
+      <c r="I91" s="98"/>
+      <c r="J91" s="98"/>
+      <c r="K91" s="98"/>
+      <c r="L91" s="99"/>
     </row>
     <row r="92" spans="2:13" s="57" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="122" t="s">
+      <c r="B92" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="123"/>
+      <c r="C92" s="101"/>
       <c r="D92" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="E92" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="F92" s="123"/>
+      <c r="E92" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="F92" s="101"/>
       <c r="G92" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="H92" s="124" t="s">
+      <c r="H92" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="I92" s="124"/>
+      <c r="I92" s="102"/>
       <c r="J92" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="K92" s="124" t="s">
+      <c r="K92" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="L92" s="125"/>
+      <c r="L92" s="103"/>
     </row>
     <row r="93" spans="2:13" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="142">
+      <c r="B93" s="79">
         <v>46142</v>
       </c>
-      <c r="C93" s="143"/>
+      <c r="C93" s="80"/>
       <c r="D93" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E93" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="F93" s="138"/>
+      <c r="E93" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="F93" s="91"/>
       <c r="G93" s="55">
         <v>1</v>
       </c>
-      <c r="H93" s="139">
+      <c r="H93" s="82">
         <f>L41</f>
         <v>0</v>
       </c>
-      <c r="I93" s="139"/>
+      <c r="I93" s="82"/>
       <c r="J93" s="56"/>
-      <c r="K93" s="140">
+      <c r="K93" s="83">
         <f>IF(J93="",0,H93)</f>
         <v>0</v>
       </c>
-      <c r="L93" s="141"/>
+      <c r="L93" s="84"/>
     </row>
     <row r="94" spans="2:13" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="136"/>
-      <c r="C94" s="137"/>
+      <c r="B94" s="92"/>
+      <c r="C94" s="93"/>
       <c r="D94" s="7"/>
-      <c r="E94" s="138"/>
-      <c r="F94" s="138"/>
+      <c r="E94" s="91"/>
+      <c r="F94" s="91"/>
       <c r="G94" s="55"/>
-      <c r="H94" s="139"/>
-      <c r="I94" s="139"/>
+      <c r="H94" s="82"/>
+      <c r="I94" s="82"/>
       <c r="J94" s="56"/>
-      <c r="K94" s="140">
+      <c r="K94" s="83">
         <f t="shared" ref="K94:K113" si="2">IF(J94="",0,H94)</f>
         <v>0</v>
       </c>
-      <c r="L94" s="141"/>
+      <c r="L94" s="84"/>
     </row>
     <row r="95" spans="2:13" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="136"/>
-      <c r="C95" s="137"/>
+      <c r="B95" s="92"/>
+      <c r="C95" s="93"/>
       <c r="D95" s="7"/>
-      <c r="E95" s="138"/>
-      <c r="F95" s="138"/>
+      <c r="E95" s="91"/>
+      <c r="F95" s="91"/>
       <c r="G95" s="55"/>
-      <c r="H95" s="139"/>
-      <c r="I95" s="139"/>
+      <c r="H95" s="82"/>
+      <c r="I95" s="82"/>
       <c r="J95" s="56"/>
-      <c r="K95" s="140">
+      <c r="K95" s="83">
         <f>IF(J95="",0,H95)</f>
         <v>0</v>
       </c>
-      <c r="L95" s="141"/>
+      <c r="L95" s="84"/>
     </row>
     <row r="96" spans="2:13" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="142"/>
-      <c r="C96" s="143"/>
+      <c r="B96" s="79"/>
+      <c r="C96" s="80"/>
       <c r="D96" s="7"/>
-      <c r="E96" s="138"/>
-      <c r="F96" s="138"/>
+      <c r="E96" s="91"/>
+      <c r="F96" s="91"/>
       <c r="G96" s="55"/>
-      <c r="H96" s="139"/>
-      <c r="I96" s="139"/>
+      <c r="H96" s="82"/>
+      <c r="I96" s="82"/>
       <c r="J96" s="56"/>
-      <c r="K96" s="140">
+      <c r="K96" s="83">
         <f t="shared" ref="K96:K100" si="3">IF(J96="",0,H96)</f>
         <v>0</v>
       </c>
-      <c r="L96" s="141"/>
+      <c r="L96" s="84"/>
     </row>
     <row r="97" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="136"/>
-      <c r="C97" s="137"/>
+      <c r="B97" s="92"/>
+      <c r="C97" s="93"/>
       <c r="D97" s="7"/>
-      <c r="E97" s="138"/>
-      <c r="F97" s="138"/>
+      <c r="E97" s="91"/>
+      <c r="F97" s="91"/>
       <c r="G97" s="55"/>
-      <c r="H97" s="139"/>
-      <c r="I97" s="139"/>
+      <c r="H97" s="82"/>
+      <c r="I97" s="82"/>
       <c r="J97" s="56"/>
-      <c r="K97" s="140">
+      <c r="K97" s="83">
         <f>IF(J97="",0,H97)</f>
         <v>0</v>
       </c>
-      <c r="L97" s="141"/>
+      <c r="L97" s="84"/>
     </row>
     <row r="98" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="136"/>
-      <c r="C98" s="137"/>
+      <c r="B98" s="92"/>
+      <c r="C98" s="93"/>
       <c r="D98" s="7"/>
-      <c r="E98" s="138"/>
-      <c r="F98" s="138"/>
+      <c r="E98" s="91"/>
+      <c r="F98" s="91"/>
       <c r="G98" s="55"/>
-      <c r="H98" s="139"/>
-      <c r="I98" s="139"/>
+      <c r="H98" s="82"/>
+      <c r="I98" s="82"/>
       <c r="J98" s="56"/>
-      <c r="K98" s="140">
+      <c r="K98" s="83">
         <f>IF(J98="",0,H98)</f>
         <v>0</v>
       </c>
-      <c r="L98" s="141"/>
+      <c r="L98" s="84"/>
     </row>
     <row r="99" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="142"/>
-      <c r="C99" s="143"/>
+      <c r="B99" s="79"/>
+      <c r="C99" s="80"/>
       <c r="D99" s="7"/>
-      <c r="E99" s="138"/>
-      <c r="F99" s="138"/>
+      <c r="E99" s="91"/>
+      <c r="F99" s="91"/>
       <c r="G99" s="55"/>
-      <c r="H99" s="139"/>
-      <c r="I99" s="139"/>
+      <c r="H99" s="82"/>
+      <c r="I99" s="82"/>
       <c r="J99" s="56"/>
-      <c r="K99" s="140">
+      <c r="K99" s="83">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L99" s="141"/>
+      <c r="L99" s="84"/>
     </row>
     <row r="100" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="142"/>
-      <c r="C100" s="143"/>
+      <c r="B100" s="79"/>
+      <c r="C100" s="80"/>
       <c r="D100" s="7"/>
-      <c r="E100" s="144"/>
-      <c r="F100" s="144"/>
+      <c r="E100" s="81"/>
+      <c r="F100" s="81"/>
       <c r="G100" s="55"/>
-      <c r="H100" s="139"/>
-      <c r="I100" s="139"/>
+      <c r="H100" s="82"/>
+      <c r="I100" s="82"/>
       <c r="J100" s="56"/>
-      <c r="K100" s="140">
+      <c r="K100" s="83">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L100" s="141"/>
+      <c r="L100" s="84"/>
     </row>
     <row r="101" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="142"/>
-      <c r="C101" s="143"/>
+      <c r="B101" s="79"/>
+      <c r="C101" s="80"/>
       <c r="D101" s="7"/>
-      <c r="E101" s="138"/>
-      <c r="F101" s="138"/>
+      <c r="E101" s="91"/>
+      <c r="F101" s="91"/>
       <c r="G101" s="55"/>
-      <c r="H101" s="139"/>
-      <c r="I101" s="139"/>
+      <c r="H101" s="82"/>
+      <c r="I101" s="82"/>
       <c r="J101" s="56"/>
-      <c r="K101" s="140">
+      <c r="K101" s="83">
         <f>IF(J101="",0,H101)</f>
         <v>0</v>
       </c>
-      <c r="L101" s="141"/>
+      <c r="L101" s="84"/>
     </row>
     <row r="102" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="142"/>
-      <c r="C102" s="143"/>
+      <c r="B102" s="79"/>
+      <c r="C102" s="80"/>
       <c r="D102" s="7"/>
-      <c r="E102" s="138"/>
-      <c r="F102" s="138"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
       <c r="G102" s="55"/>
-      <c r="H102" s="139"/>
-      <c r="I102" s="139"/>
+      <c r="H102" s="82"/>
+      <c r="I102" s="82"/>
       <c r="J102" s="56"/>
-      <c r="K102" s="140">
+      <c r="K102" s="83">
         <f t="shared" ref="K102:K104" si="4">IF(J102="",0,H102)</f>
         <v>0</v>
       </c>
-      <c r="L102" s="141"/>
+      <c r="L102" s="84"/>
     </row>
     <row r="103" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="142"/>
-      <c r="C103" s="143"/>
+      <c r="B103" s="79"/>
+      <c r="C103" s="80"/>
       <c r="D103" s="7"/>
-      <c r="E103" s="138"/>
-      <c r="F103" s="138"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="91"/>
       <c r="G103" s="55"/>
-      <c r="H103" s="139"/>
-      <c r="I103" s="139"/>
+      <c r="H103" s="82"/>
+      <c r="I103" s="82"/>
       <c r="J103" s="56"/>
-      <c r="K103" s="140">
+      <c r="K103" s="83">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L103" s="141"/>
+      <c r="L103" s="84"/>
     </row>
     <row r="104" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="142"/>
-      <c r="C104" s="143"/>
+      <c r="B104" s="79"/>
+      <c r="C104" s="80"/>
       <c r="D104" s="7"/>
-      <c r="E104" s="144"/>
-      <c r="F104" s="144"/>
+      <c r="E104" s="81"/>
+      <c r="F104" s="81"/>
       <c r="G104" s="55"/>
-      <c r="H104" s="139"/>
-      <c r="I104" s="139"/>
+      <c r="H104" s="82"/>
+      <c r="I104" s="82"/>
       <c r="J104" s="56"/>
-      <c r="K104" s="140">
+      <c r="K104" s="83">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L104" s="141"/>
+      <c r="L104" s="84"/>
     </row>
     <row r="105" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="142"/>
-      <c r="C105" s="143"/>
+      <c r="B105" s="79"/>
+      <c r="C105" s="80"/>
       <c r="D105" s="7"/>
-      <c r="E105" s="138"/>
-      <c r="F105" s="138"/>
+      <c r="E105" s="91"/>
+      <c r="F105" s="91"/>
       <c r="G105" s="55"/>
-      <c r="H105" s="139"/>
-      <c r="I105" s="139"/>
+      <c r="H105" s="82"/>
+      <c r="I105" s="82"/>
       <c r="J105" s="56"/>
-      <c r="K105" s="140">
+      <c r="K105" s="83">
         <f>IF(J105="",0,H105)</f>
         <v>0</v>
       </c>
-      <c r="L105" s="141"/>
+      <c r="L105" s="84"/>
     </row>
     <row r="106" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="142"/>
-      <c r="C106" s="143"/>
+      <c r="B106" s="79"/>
+      <c r="C106" s="80"/>
       <c r="D106" s="7"/>
-      <c r="E106" s="138"/>
-      <c r="F106" s="138"/>
+      <c r="E106" s="91"/>
+      <c r="F106" s="91"/>
       <c r="G106" s="55"/>
-      <c r="H106" s="139"/>
-      <c r="I106" s="139"/>
+      <c r="H106" s="82"/>
+      <c r="I106" s="82"/>
       <c r="J106" s="56"/>
-      <c r="K106" s="140">
+      <c r="K106" s="83">
         <f t="shared" ref="K106:K108" si="5">IF(J106="",0,H106)</f>
         <v>0</v>
       </c>
-      <c r="L106" s="141"/>
+      <c r="L106" s="84"/>
     </row>
     <row r="107" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="142"/>
-      <c r="C107" s="143"/>
+      <c r="B107" s="79"/>
+      <c r="C107" s="80"/>
       <c r="D107" s="7"/>
-      <c r="E107" s="138"/>
-      <c r="F107" s="138"/>
+      <c r="E107" s="91"/>
+      <c r="F107" s="91"/>
       <c r="G107" s="55"/>
-      <c r="H107" s="139"/>
-      <c r="I107" s="139"/>
+      <c r="H107" s="82"/>
+      <c r="I107" s="82"/>
       <c r="J107" s="56"/>
-      <c r="K107" s="140">
+      <c r="K107" s="83">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L107" s="141"/>
+      <c r="L107" s="84"/>
     </row>
     <row r="108" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="142"/>
-      <c r="C108" s="143"/>
+      <c r="B108" s="79"/>
+      <c r="C108" s="80"/>
       <c r="D108" s="7"/>
-      <c r="E108" s="144"/>
-      <c r="F108" s="144"/>
+      <c r="E108" s="81"/>
+      <c r="F108" s="81"/>
       <c r="G108" s="55"/>
-      <c r="H108" s="139"/>
-      <c r="I108" s="139"/>
+      <c r="H108" s="82"/>
+      <c r="I108" s="82"/>
       <c r="J108" s="56"/>
-      <c r="K108" s="140">
+      <c r="K108" s="83">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L108" s="141"/>
+      <c r="L108" s="84"/>
     </row>
     <row r="109" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="142"/>
-      <c r="C109" s="143"/>
+      <c r="B109" s="79"/>
+      <c r="C109" s="80"/>
       <c r="D109" s="7"/>
-      <c r="E109" s="138"/>
-      <c r="F109" s="138"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
       <c r="G109" s="55"/>
-      <c r="H109" s="139"/>
-      <c r="I109" s="139"/>
+      <c r="H109" s="82"/>
+      <c r="I109" s="82"/>
       <c r="J109" s="56"/>
-      <c r="K109" s="140">
+      <c r="K109" s="83">
         <f>IF(J109="",0,H109)</f>
         <v>0</v>
       </c>
-      <c r="L109" s="141"/>
+      <c r="L109" s="84"/>
     </row>
     <row r="110" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B110" s="142"/>
-      <c r="C110" s="143"/>
+      <c r="B110" s="79"/>
+      <c r="C110" s="80"/>
       <c r="D110" s="7"/>
-      <c r="E110" s="138"/>
-      <c r="F110" s="138"/>
+      <c r="E110" s="91"/>
+      <c r="F110" s="91"/>
       <c r="G110" s="55"/>
-      <c r="H110" s="139"/>
-      <c r="I110" s="139"/>
+      <c r="H110" s="82"/>
+      <c r="I110" s="82"/>
       <c r="J110" s="56"/>
-      <c r="K110" s="140">
+      <c r="K110" s="83">
         <f t="shared" ref="K110" si="6">IF(J110="",0,H110)</f>
         <v>0</v>
       </c>
-      <c r="L110" s="141"/>
+      <c r="L110" s="84"/>
     </row>
     <row r="111" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="142"/>
-      <c r="C111" s="143"/>
+      <c r="B111" s="79"/>
+      <c r="C111" s="80"/>
       <c r="D111" s="7"/>
-      <c r="E111" s="138"/>
-      <c r="F111" s="138"/>
+      <c r="E111" s="91"/>
+      <c r="F111" s="91"/>
       <c r="G111" s="55"/>
-      <c r="H111" s="139"/>
-      <c r="I111" s="139"/>
+      <c r="H111" s="82"/>
+      <c r="I111" s="82"/>
       <c r="J111" s="56"/>
-      <c r="K111" s="140">
+      <c r="K111" s="83">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L111" s="141"/>
+      <c r="L111" s="84"/>
     </row>
     <row r="112" spans="2:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="142"/>
-      <c r="C112" s="143"/>
+      <c r="B112" s="79"/>
+      <c r="C112" s="80"/>
       <c r="D112" s="7"/>
-      <c r="E112" s="144"/>
-      <c r="F112" s="144"/>
+      <c r="E112" s="81"/>
+      <c r="F112" s="81"/>
       <c r="G112" s="55"/>
-      <c r="H112" s="139"/>
-      <c r="I112" s="139"/>
+      <c r="H112" s="82"/>
+      <c r="I112" s="82"/>
       <c r="J112" s="56"/>
-      <c r="K112" s="140">
+      <c r="K112" s="83">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L112" s="141"/>
+      <c r="L112" s="84"/>
     </row>
     <row r="113" spans="1:12" s="6" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="142"/>
-      <c r="C113" s="143"/>
+      <c r="B113" s="79"/>
+      <c r="C113" s="80"/>
       <c r="D113" s="7"/>
-      <c r="E113" s="144"/>
-      <c r="F113" s="144"/>
+      <c r="E113" s="81"/>
+      <c r="F113" s="81"/>
       <c r="G113" s="55"/>
-      <c r="H113" s="139"/>
-      <c r="I113" s="139"/>
+      <c r="H113" s="82"/>
+      <c r="I113" s="82"/>
       <c r="J113" s="56"/>
-      <c r="K113" s="140">
+      <c r="K113" s="83">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L113" s="141"/>
+      <c r="L113" s="84"/>
     </row>
     <row r="114" spans="1:12" s="60" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="155" t="s">
+      <c r="B114" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="156"/>
-      <c r="D114" s="156"/>
-      <c r="E114" s="156"/>
-      <c r="F114" s="156"/>
-      <c r="G114" s="157"/>
-      <c r="H114" s="158">
+      <c r="C114" s="86"/>
+      <c r="D114" s="86"/>
+      <c r="E114" s="86"/>
+      <c r="F114" s="86"/>
+      <c r="G114" s="87"/>
+      <c r="H114" s="88">
         <f>SUM(H93:H113)</f>
         <v>0</v>
       </c>
-      <c r="I114" s="158"/>
-      <c r="J114" s="159">
+      <c r="I114" s="88"/>
+      <c r="J114" s="89">
         <f>SUM(K93:K113)</f>
         <v>0</v>
       </c>
-      <c r="K114" s="159"/>
-      <c r="L114" s="160"/>
+      <c r="K114" s="89"/>
+      <c r="L114" s="90"/>
     </row>
     <row r="115" spans="1:12" s="42" customFormat="1" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="40"/>
@@ -3763,25 +3763,25 @@
       <c r="K115" s="40"/>
     </row>
     <row r="116" spans="1:12" s="57" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B116" s="145" t="s">
+      <c r="B116" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C116" s="146"/>
-      <c r="D116" s="146"/>
-      <c r="E116" s="146"/>
-      <c r="F116" s="146"/>
-      <c r="G116" s="146"/>
-      <c r="H116" s="147">
+      <c r="C116" s="70"/>
+      <c r="D116" s="70"/>
+      <c r="E116" s="70"/>
+      <c r="F116" s="70"/>
+      <c r="G116" s="70"/>
+      <c r="H116" s="71">
         <f>IFERROR(SUM(L65:L73)/J114-100%,0)</f>
         <v>0</v>
       </c>
-      <c r="I116" s="148"/>
-      <c r="J116" s="149">
+      <c r="I116" s="72"/>
+      <c r="J116" s="73">
         <f>SUM(L65:L73)-J114</f>
         <v>0</v>
       </c>
-      <c r="K116" s="150"/>
-      <c r="L116" s="151"/>
+      <c r="K116" s="74"/>
+      <c r="L116" s="75"/>
     </row>
     <row r="117" spans="1:12" s="42" customFormat="1" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="40"/>
@@ -3797,188 +3797,40 @@
       <c r="K117" s="40"/>
     </row>
     <row r="118" spans="1:12" s="57" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B118" s="145" t="s">
+      <c r="B118" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="C118" s="146"/>
-      <c r="D118" s="146"/>
-      <c r="E118" s="146"/>
-      <c r="F118" s="146"/>
-      <c r="G118" s="146"/>
-      <c r="H118" s="147">
+      <c r="C118" s="70"/>
+      <c r="D118" s="70"/>
+      <c r="E118" s="70"/>
+      <c r="F118" s="70"/>
+      <c r="G118" s="70"/>
+      <c r="H118" s="71">
         <f>IFERROR(L62/H114-100%,0)</f>
         <v>0</v>
       </c>
-      <c r="I118" s="148"/>
-      <c r="J118" s="152">
+      <c r="I118" s="72"/>
+      <c r="J118" s="76">
         <f>L62-H114</f>
         <v>0</v>
       </c>
-      <c r="K118" s="153"/>
-      <c r="L118" s="154"/>
+      <c r="K118" s="77"/>
+      <c r="L118" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="193">
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="H116:I116"/>
-    <mergeCell ref="J116:L116"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="H118:I118"/>
-    <mergeCell ref="J118:L118"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="H113:I113"/>
-    <mergeCell ref="K113:L113"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="H114:I114"/>
-    <mergeCell ref="J114:L114"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="H111:I111"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="H112:I112"/>
-    <mergeCell ref="K112:L112"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="H109:I109"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="H110:I110"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="H107:I107"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="H108:I108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="H105:I105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="H106:I106"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="H103:I103"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="H104:I104"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="H101:I101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="H102:I102"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="H99:I99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="H100:I100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="H95:I95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="H96:I96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="H98:I98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="H93:I93"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="H97:I97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="B87:G87"/>
-    <mergeCell ref="H87:L87"/>
-    <mergeCell ref="B91:L91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="H92:I92"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="B74:K74"/>
-    <mergeCell ref="B75:K75"/>
-    <mergeCell ref="B85:G85"/>
-    <mergeCell ref="H85:L85"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="H86:L86"/>
-    <mergeCell ref="B77:L77"/>
-    <mergeCell ref="B78:L78"/>
-    <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B82:L82"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="E71:K71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="E72:K72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="E73:K73"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="E68:K68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="E69:K69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="E70:K70"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="E65:K65"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="E66:K66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="E67:K67"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="B58:K58"/>
-    <mergeCell ref="B60:K60"/>
-    <mergeCell ref="B61:K61"/>
-    <mergeCell ref="B62:K62"/>
-    <mergeCell ref="B64:L64"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C54:I54"/>
-    <mergeCell ref="C55:I55"/>
-    <mergeCell ref="C56:I56"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="B46:B57"/>
-    <mergeCell ref="C46:I46"/>
-    <mergeCell ref="C47:I47"/>
-    <mergeCell ref="C48:I48"/>
-    <mergeCell ref="C49:I49"/>
-    <mergeCell ref="C50:I50"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C51:I51"/>
-    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="B2:H4"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="B7:L7"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C25:I25"/>
@@ -4000,18 +3852,166 @@
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C38:I38"/>
     <mergeCell ref="C39:I39"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="B2:H4"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B6:L6"/>
-    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C31:I31"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C51:I51"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C54:I54"/>
+    <mergeCell ref="C55:I55"/>
+    <mergeCell ref="C56:I56"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="B44:L44"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="C48:I48"/>
+    <mergeCell ref="C49:I49"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="E65:K65"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="E66:K66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="E67:K67"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B58:K58"/>
+    <mergeCell ref="B60:K60"/>
+    <mergeCell ref="B61:K61"/>
+    <mergeCell ref="B62:K62"/>
+    <mergeCell ref="B64:L64"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="E71:K71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="E72:K72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="E73:K73"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="E68:K68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="E69:K69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="E70:K70"/>
+    <mergeCell ref="B87:G87"/>
+    <mergeCell ref="H87:L87"/>
+    <mergeCell ref="B91:L91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="B74:K74"/>
+    <mergeCell ref="B75:K75"/>
+    <mergeCell ref="B85:G85"/>
+    <mergeCell ref="H85:L85"/>
+    <mergeCell ref="B86:G86"/>
+    <mergeCell ref="H86:L86"/>
+    <mergeCell ref="B77:L77"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B79:L79"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="H97:I97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="H95:I95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="H103:I103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="H104:I104"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="H102:I102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="H107:I107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="H105:I105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="H106:I106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="H111:I111"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="H112:I112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="H109:I109"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="H110:I110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="H116:I116"/>
+    <mergeCell ref="J116:L116"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="H118:I118"/>
+    <mergeCell ref="J118:L118"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="H113:I113"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="H114:I114"/>
+    <mergeCell ref="J114:L114"/>
   </mergeCells>
   <conditionalFormatting sqref="H116">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">

--- a/Templates/GZ28 V8 SpeedShop INVOICE US.000.1 - BLANK.xlsx
+++ b/Templates/GZ28 V8 SpeedShop INVOICE US.000.1 - BLANK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\gz28-speedshop-control\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4FA691-D62F-46CA-9C17-1D92C316F99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE71D715-6143-4FDB-94D7-057EC8AC48A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="583" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,7 +388,7 @@
     <t>INVOICE #</t>
   </si>
   <si>
-    <t>Sercice:</t>
+    <t>Service:</t>
   </si>
 </sst>
 </file>
